--- a/sample_data/KE/inventory_2025-10.xlsx
+++ b/sample_data/KE/inventory_2025-10.xlsx
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="D188" t="n">
-        <v>100</v>
+        <v>-20</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
